--- a/output/pdf_financials_xlsx/SHOP.xlsx
+++ b/output/pdf_financials_xlsx/SHOP.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>15.356</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000241</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3140.592</v>
+        <v>3125.236</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.003623</v>
+        <v>-0.003698</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.000185</v>
+        <v>-5.6e-05</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3206.9</v>
+        <v>3191.544</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.00353</v>
+        <v>-0.003605</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.000255</v>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>69.53599592008077</v>
+        <v>69.20302802169019</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-63.03571428571428</v>
+        <v>-64.375</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.611898016997167</v>
+        <v>0.198300283286119</v>
       </c>
     </row>
     <row r="31">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">

--- a/output/pdf_financials_xlsx/SHOP.xlsx
+++ b/output/pdf_financials_xlsx/SHOP.xlsx
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>192.209</v>
+        <v>205.209</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.000273</v>
+        <v>23.000273</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.000282</v>
+        <v>27.000282</v>
       </c>
     </row>
     <row r="42">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>15.748</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>18.161</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>15.748</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>18.161</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>29.253</v>
+        <v>13.505</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>856.007162</v>
+        <v>837.846162</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -1725,15 +1725,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.001414490043914042</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>2204.272363150868</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -2269,13 +2265,13 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-7337.366</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.005011</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.005841</v>
       </c>
     </row>
     <row r="115">
@@ -4143,7 +4139,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>15.748</v>
       </c>
@@ -4610,7 +4610,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5005,7 +5009,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5992,7 +6000,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>-7337.366</v>
       </c>
